--- a/data/trans_orig/IP18A02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP18A02-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>30725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30847</t>
+          <t>29563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48409</t>
+          <t>48490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63249</t>
+          <t>63780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>77315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>64576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75905</t>
+          <t>76200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132210</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149772</t>
+          <t>151056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24581</t>
+          <t>25307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46360</t>
+          <t>47038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>54978</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67566</t>
+          <t>66636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50753</t>
+          <t>49922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61791</t>
+          <t>61976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109293</t>
+          <t>108615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126032</t>
+          <t>126137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19388</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>23261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39629</t>
+          <t>38991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40701</t>
+          <t>40569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>51156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61558</t>
+          <t>61566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73518</t>
+          <t>73760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105949</t>
+          <t>106587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122487</t>
+          <t>122317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54981</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30564</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48613</t>
+          <t>47729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>71897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97632</t>
+          <t>98342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117452</t>
+          <t>118453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135933</t>
+          <t>136283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127869</t>
+          <t>128753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145918</t>
+          <t>146010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>251282</t>
+          <t>250572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277326</t>
+          <t>277017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>26159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22628</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>26671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43109</t>
+          <t>43762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58958</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72087</t>
+          <t>72404</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92457</t>
+          <t>92452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145429</t>
+          <t>144776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>161915</t>
+          <t>161867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17342</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>19283</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>34262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48900</t>
+          <t>49017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59424</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49035</t>
+          <t>48754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59014</t>
+          <t>58976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101029</t>
+          <t>100885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116686</t>
+          <t>115864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>119742</t>
+          <t>120188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153487</t>
+          <t>151149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>102815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131582</t>
+          <t>134049</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230074</t>
+          <t>231118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>273861</t>
+          <t>276975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>408433</t>
+          <t>410771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>442178</t>
+          <t>441732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>460946</t>
+          <t>458479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>490561</t>
+          <t>489713</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>880587</t>
+          <t>877473</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>924374</t>
+          <t>923330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26494</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40609</t>
+          <t>40201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63556</t>
+          <t>63467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73906</t>
+          <t>74326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>60122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72532</t>
+          <t>72900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127486</t>
+          <t>127894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144131</t>
+          <t>144412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26286</t>
+          <t>27512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47533</t>
+          <t>47463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64331</t>
+          <t>64593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76940</t>
+          <t>77141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62673</t>
+          <t>61447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75242</t>
+          <t>74812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131382</t>
+          <t>131452</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148435</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32192</t>
+          <t>32537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60327</t>
+          <t>59787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71057</t>
+          <t>71417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>65909</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76787</t>
+          <t>76507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130873</t>
+          <t>130528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145391</t>
+          <t>145288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35066</t>
+          <t>34886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54235</t>
+          <t>55444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38731</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58954</t>
+          <t>58541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105985</t>
+          <t>106503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138104</t>
+          <t>136895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157273</t>
+          <t>157453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156586</t>
+          <t>156999</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176809</t>
+          <t>176703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301894</t>
+          <t>301376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>329793</t>
+          <t>329579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37554</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>27294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>39086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98048</t>
+          <t>97767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113660</t>
+          <t>113692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106707</t>
+          <t>105951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120696</t>
+          <t>119969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210496</t>
+          <t>208142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230323</t>
+          <t>229761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35226</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32801</t>
+          <t>32550</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43823</t>
+          <t>42987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50188</t>
+          <t>50925</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61294</t>
+          <t>61245</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86943</t>
+          <t>86969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>102538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115633</t>
+          <t>115642</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147961</t>
+          <t>149401</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113686</t>
+          <t>113380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148289</t>
+          <t>147430</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>236820</t>
+          <t>237633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>287930</t>
+          <t>286527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>484231</t>
+          <t>482791</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>516559</t>
+          <t>516550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>528490</t>
+          <t>529349</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>563093</t>
+          <t>563399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1021040</t>
+          <t>1022443</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1072150</t>
+          <t>1071337</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>26102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>25105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28953</t>
+          <t>28878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45849</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50597</t>
+          <t>49244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62856</t>
+          <t>62167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68155</t>
+          <t>67846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80022</t>
+          <t>80333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122448</t>
+          <t>122451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139344</t>
+          <t>139419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26666</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>34190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>53054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70267</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82645</t>
+          <t>83276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68339</t>
+          <t>68615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81746</t>
+          <t>81954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142959</t>
+          <t>142482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161634</t>
+          <t>161346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>15496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18499</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>32765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46733</t>
+          <t>46594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46444</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57648</t>
+          <t>57517</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87508</t>
+          <t>87637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101790</t>
+          <t>101903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28090</t>
+          <t>27587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44502</t>
+          <t>45467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39587</t>
+          <t>39560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>54404</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79265</t>
+          <t>79866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161430</t>
+          <t>160465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177842</t>
+          <t>178345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148216</t>
+          <t>148243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165063</t>
+          <t>164741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314470</t>
+          <t>313869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339385</t>
+          <t>339331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>27984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54660</t>
+          <t>55024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94950</t>
+          <t>94657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108086</t>
+          <t>107913</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97472</t>
+          <t>97567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111716</t>
+          <t>112429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196381</t>
+          <t>196017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217043</t>
+          <t>216275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>19132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>19592</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37635</t>
+          <t>37176</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47559</t>
+          <t>47844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52289</t>
+          <t>52246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>82736</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96809</t>
+          <t>96415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104984</t>
+          <t>103932</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134965</t>
+          <t>134314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108144</t>
+          <t>106878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140812</t>
+          <t>140542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>220884</t>
+          <t>219462</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265410</t>
+          <t>265619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475093</t>
+          <t>475744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>505074</t>
+          <t>506126</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>495415</t>
+          <t>495685</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>528083</t>
+          <t>529349</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>980875</t>
+          <t>980666</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1025401</t>
+          <t>1026823</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18555</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23799</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>41887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24626</t>
+          <t>24624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>28191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36251</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50990</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62174</t>
+          <t>61710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>14088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>22196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>45216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>14854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>20180</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>24991</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32499</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33279</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52240</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73621</t>
+          <t>73688</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86677</t>
+          <t>86516</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>97863</t>
+          <t>97613</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112450</t>
+          <t>113590</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>176802</t>
+          <t>176887</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>195763</t>
+          <t>196152</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
